--- a/data/external/vsa_prices.xlsx
+++ b/data/external/vsa_prices.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Các vấn đề hiện đại trong KHMT\Code\BTL_NV-H-KHMT\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{3D31834B-7A1A-4E24-A4F2-684ABD6EF16E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E6B357A-989C-46F0-8531-02752AAD0BDF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{373B9F1D-2389-4102-BE20-9482FA60DE4D}"/>
+    <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="12336" xr2:uid="{373B9F1D-2389-4102-BE20-9482FA60DE4D}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="53">
   <si>
     <t>phôi thép</t>
   </si>
@@ -195,6 +195,15 @@
   </si>
   <si>
     <t>350-366</t>
+  </si>
+  <si>
+    <t>282.5</t>
+  </si>
+  <si>
+    <t>402-405</t>
+  </si>
+  <si>
+    <t>375-380</t>
   </si>
 </sst>
 </file>
@@ -1326,120 +1335,336 @@
       <c r="A50" s="2">
         <v>44927</v>
       </c>
+      <c r="C50" s="1">
+        <v>596</v>
+      </c>
+      <c r="D50" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="E50" s="1" t="s">
+        <v>50</v>
+      </c>
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A51" s="2">
         <v>44958</v>
       </c>
+      <c r="C51" s="1">
+        <v>619</v>
+      </c>
+      <c r="D51" s="1">
+        <v>435</v>
+      </c>
+      <c r="E51" s="1">
+        <v>325</v>
+      </c>
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A52" s="2">
         <v>44986</v>
       </c>
+      <c r="C52" s="1">
+        <v>643</v>
+      </c>
+      <c r="D52" s="1">
+        <v>448</v>
+      </c>
+      <c r="E52" s="1">
+        <v>331</v>
+      </c>
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A53" s="2">
         <v>45017</v>
       </c>
+      <c r="C53" s="1">
+        <v>648</v>
+      </c>
+      <c r="D53" s="1">
+        <v>448</v>
+      </c>
+      <c r="E53" s="1">
+        <v>260</v>
+      </c>
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A54" s="2">
         <v>45047</v>
       </c>
+      <c r="C54" s="1">
+        <v>605</v>
+      </c>
+      <c r="D54" s="1">
+        <v>405</v>
+      </c>
+      <c r="E54" s="1">
+        <v>241</v>
+      </c>
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A55" s="2">
         <v>45078</v>
       </c>
+      <c r="C55" s="1">
+        <v>606.49</v>
+      </c>
+      <c r="D55" s="1">
+        <v>399.86</v>
+      </c>
+      <c r="E55" s="1">
+        <v>233.91</v>
+      </c>
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A56" s="2">
         <v>45108</v>
       </c>
+      <c r="C56" s="1">
+        <v>571</v>
+      </c>
+      <c r="D56" s="1">
+        <v>375</v>
+      </c>
+      <c r="E56" s="1">
+        <v>230</v>
+      </c>
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A57" s="2">
         <v>45139</v>
       </c>
+      <c r="C57" s="1">
+        <v>556</v>
+      </c>
+      <c r="D57" s="1">
+        <v>368</v>
+      </c>
+      <c r="E57" s="1">
+        <v>305</v>
+      </c>
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A58" s="2">
         <v>45170</v>
       </c>
+      <c r="C58" s="1">
+        <v>537</v>
+      </c>
+      <c r="D58" s="1">
+        <v>387</v>
+      </c>
+      <c r="E58" s="1">
+        <v>305</v>
+      </c>
     </row>
     <row r="59" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A59" s="2">
         <v>45200</v>
       </c>
+      <c r="C59" s="1">
+        <v>530</v>
+      </c>
+      <c r="D59" s="1">
+        <v>385</v>
+      </c>
+      <c r="E59" s="1">
+        <v>325</v>
+      </c>
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A60" s="2">
         <v>45231</v>
       </c>
+      <c r="C60" s="1">
+        <v>532</v>
+      </c>
+      <c r="D60" s="1">
+        <v>372</v>
+      </c>
+      <c r="E60" s="1">
+        <v>272</v>
+      </c>
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A61" s="2">
         <v>45261</v>
       </c>
+      <c r="C61" s="1">
+        <v>558</v>
+      </c>
+      <c r="D61" s="1">
+        <v>391</v>
+      </c>
+      <c r="E61" s="1">
+        <v>279</v>
+      </c>
     </row>
     <row r="62" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A62" s="2">
         <v>45292</v>
       </c>
+      <c r="C62" s="1">
+        <v>480</v>
+      </c>
+      <c r="D62" s="1">
+        <v>397</v>
+      </c>
+      <c r="E62" s="1">
+        <v>275</v>
+      </c>
     </row>
     <row r="63" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A63" s="2">
         <v>45323</v>
       </c>
+      <c r="C63" s="1">
+        <v>600</v>
+      </c>
+      <c r="D63" s="1">
+        <v>382</v>
+      </c>
+      <c r="E63" s="1">
+        <v>315</v>
+      </c>
     </row>
     <row r="64" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A64" s="2">
         <v>45352</v>
       </c>
-    </row>
-    <row r="65" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="C64" s="1">
+        <v>602</v>
+      </c>
+      <c r="D64" s="1">
+        <v>385</v>
+      </c>
+      <c r="E64" s="1">
+        <v>306.5</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A65" s="2">
         <v>45383</v>
       </c>
-    </row>
-    <row r="66" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="C65" s="1">
+        <v>542</v>
+      </c>
+      <c r="D65" s="1">
+        <v>375</v>
+      </c>
+      <c r="E65" s="1">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A66" s="2">
         <v>45413</v>
       </c>
-    </row>
-    <row r="67" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="C66" s="1">
+        <v>531</v>
+      </c>
+      <c r="D66" s="1">
+        <v>400</v>
+      </c>
+      <c r="E66" s="1">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A67" s="2">
         <v>45444</v>
       </c>
-    </row>
-    <row r="68" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="C67" s="1">
+        <v>546</v>
+      </c>
+      <c r="D67" s="1">
+        <v>375</v>
+      </c>
+      <c r="E67" s="1">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A68" s="2">
         <v>45474</v>
       </c>
-    </row>
-    <row r="69" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="C68" s="1">
+        <v>531</v>
+      </c>
+      <c r="D68" s="1">
+        <v>380</v>
+      </c>
+      <c r="E68" s="1">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A69" s="2">
         <v>45505</v>
       </c>
-    </row>
-    <row r="70" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="C69" s="1">
+        <v>504</v>
+      </c>
+      <c r="D69" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="E69" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A70" s="2">
         <v>45536</v>
       </c>
-    </row>
-    <row r="71" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="C70" s="1">
+        <v>500</v>
+      </c>
+      <c r="D70" s="1">
+        <v>352</v>
+      </c>
+      <c r="E70" s="1">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A71" s="2">
         <v>45566</v>
       </c>
-    </row>
-    <row r="72" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="C71" s="1">
+        <v>500</v>
+      </c>
+      <c r="D71" s="1">
+        <v>354</v>
+      </c>
+      <c r="E71" s="1">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A72" s="2">
         <v>45597</v>
       </c>
-    </row>
-    <row r="73" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="C72" s="1">
+        <v>515</v>
+      </c>
+      <c r="D72" s="1">
+        <v>354</v>
+      </c>
+      <c r="E72" s="1">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A73" s="2">
         <v>45627</v>
+      </c>
+      <c r="C73" s="1">
+        <v>503</v>
+      </c>
+      <c r="D73" s="1">
+        <v>348</v>
+      </c>
+      <c r="E73" s="1">
+        <v>166</v>
       </c>
     </row>
   </sheetData>
